--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.05412</v>
+        <v>17.29815</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0852</v>
+        <v>17.10771</v>
       </c>
       <c r="E2" t="n">
-        <v>17.12321</v>
+        <v>17.15857</v>
       </c>
       <c r="F2" t="n">
-        <v>43.69325</v>
+        <v>43.3972</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05188</v>
+        <v>0.05144</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82452</v>
+        <v>1.86595</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.77811</v>
+        <v>17.17065</v>
       </c>
       <c r="D3" t="n">
-        <v>17.31995</v>
+        <v>17.08444</v>
       </c>
       <c r="E3" t="n">
-        <v>17.17843</v>
+        <v>17.12437</v>
       </c>
       <c r="F3" t="n">
-        <v>43.49206</v>
+        <v>43.71521</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05198</v>
+        <v>0.051</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8542</v>
+        <v>1.88124</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.35992</v>
+        <v>17.16761</v>
       </c>
       <c r="D4" t="n">
-        <v>17.19211</v>
+        <v>16.87853</v>
       </c>
       <c r="E4" t="n">
-        <v>17.2396</v>
+        <v>16.96701</v>
       </c>
       <c r="F4" t="n">
-        <v>43.39147</v>
+        <v>43.86983</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05131</v>
+        <v>0.05115</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9032</v>
+        <v>1.83952</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.07508</v>
+        <v>17.09167</v>
       </c>
       <c r="D6" t="n">
-        <v>16.33515</v>
+        <v>16.46919</v>
       </c>
       <c r="E6" t="n">
-        <v>16.67059</v>
+        <v>17.06574</v>
       </c>
       <c r="F6" t="n">
-        <v>22.30812</v>
+        <v>22.33671</v>
       </c>
       <c r="G6" t="n">
-        <v>34.8381</v>
+        <v>34.67419</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.09855</v>
+        <v>17.40295</v>
       </c>
       <c r="D7" t="n">
-        <v>16.52486</v>
+        <v>16.64488</v>
       </c>
       <c r="E7" t="n">
-        <v>17.08173</v>
+        <v>16.70009</v>
       </c>
       <c r="F7" t="n">
-        <v>22.65911</v>
+        <v>22.37155</v>
       </c>
       <c r="G7" t="n">
-        <v>35.66871</v>
+        <v>35.35781</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.25804</v>
+        <v>17.29314</v>
       </c>
       <c r="D8" t="n">
-        <v>16.43644</v>
+        <v>16.30865</v>
       </c>
       <c r="E8" t="n">
-        <v>17.24603</v>
+        <v>16.93295</v>
       </c>
       <c r="F8" t="n">
-        <v>22.35882</v>
+        <v>21.91212</v>
       </c>
       <c r="G8" t="n">
-        <v>34.95019</v>
+        <v>34.39754</v>
       </c>
     </row>
   </sheetData>
